--- a/결산_raw.xlsx
+++ b/결산_raw.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\주민규\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\주민규\학소자료\7월\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="7716" tabRatio="761"/>
+    <workbookView xWindow="3645" yWindow="0" windowWidth="23040" windowHeight="7710" tabRatio="761" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="결산" sheetId="12" r:id="rId1"/>
@@ -2537,11 +2537,11 @@
   <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="#,###&quot;억&quot;"/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="181" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="182" formatCode="0&quot;일&quot;"/>
-    <numFmt numFmtId="183" formatCode="#,###&quot;일&quot;"/>
+    <numFmt numFmtId="176" formatCode="#,###&quot;억&quot;"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="0&quot;일&quot;"/>
+    <numFmt numFmtId="180" formatCode="#,###&quot;일&quot;"/>
   </numFmts>
   <fonts count="30" x14ac:knownFonts="1">
     <font>
@@ -3684,7 +3684,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3710,13 +3710,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3725,76 +3725,76 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="4" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3803,7 +3803,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3833,157 +3833,157 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="16" fillId="5" borderId="33" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="16" fillId="5" borderId="33" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="16" fillId="5" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="16" fillId="5" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="4" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="4" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="16" fillId="5" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="16" fillId="5" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="16" fillId="5" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="16" fillId="5" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="16" fillId="5" borderId="39" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="16" fillId="5" borderId="39" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="39" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="39" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="4" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="4" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="4" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="4" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="19" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="19" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="20" fillId="2" borderId="43" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="20" fillId="2" borderId="43" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="20" fillId="2" borderId="31" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="20" fillId="2" borderId="31" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="20" fillId="2" borderId="44" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="20" fillId="2" borderId="44" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="20" fillId="2" borderId="45" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="20" fillId="2" borderId="45" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="19" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="19" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="20" fillId="2" borderId="48" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="20" fillId="2" borderId="48" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="21" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4043,216 +4043,228 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="24" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="24" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="2" borderId="56" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="24" fillId="2" borderId="56" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="2" borderId="58" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="24" fillId="2" borderId="58" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="26" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="26" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="26" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="26" fillId="0" borderId="62" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="26" fillId="0" borderId="62" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="26" fillId="0" borderId="61" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="26" fillId="0" borderId="61" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="4" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="4" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="26" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="26" fillId="0" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="26" fillId="0" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="26" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="26" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="26" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="26" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="2" borderId="66" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="15" fillId="2" borderId="66" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="2" borderId="64" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="15" fillId="2" borderId="64" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="5" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="5" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="5" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="5" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="24" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="24" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="2" borderId="66" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="24" fillId="2" borderId="66" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="2" borderId="64" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="24" fillId="2" borderId="64" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="2" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="2" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="2" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="2" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="2" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="2" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="24" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="24" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="2" borderId="50" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="24" fillId="2" borderId="50" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="2" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="24" fillId="2" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="27" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="27" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="27" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="27" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="27" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="27" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="27" fillId="5" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="27" fillId="5" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="27" fillId="5" borderId="45" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="27" fillId="5" borderId="45" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="27" fillId="5" borderId="44" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="27" fillId="5" borderId="44" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="27" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="27" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="183" fontId="27" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="27" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="183" fontId="27" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="27" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="27" fillId="4" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="27" fillId="4" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="27" fillId="4" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="27" fillId="4" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="183" fontId="27" fillId="4" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="27" fillId="4" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="29" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="29" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="28" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="28" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -4269,18 +4281,6 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -4596,18 +4596,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:CU64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" style="38" customWidth="1"/>
-    <col min="2" max="2" width="17.09765625" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.09765625" style="38" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.125" style="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.125" style="38" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="38" bestFit="1" customWidth="1"/>
     <col min="5" max="71" width="9" style="38"/>
     <col min="72" max="99" width="9" style="38" customWidth="1"/>
     <col min="100" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
       <c r="D2" s="37"/>
@@ -4707,8 +4707,8 @@
       <c r="CT2" s="37"/>
       <c r="CU2" s="37"/>
     </row>
-    <row r="3" spans="2:99" s="43" customFormat="1" ht="13.8" x14ac:dyDescent="0.4">
-      <c r="B3" s="193" t="s">
+    <row r="3" spans="2:99" s="43" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
+      <c r="B3" s="187" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="39"/>
@@ -5001,8 +5001,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="2:99" s="43" customFormat="1" ht="13.8" x14ac:dyDescent="0.4">
-      <c r="B4" s="194"/>
+    <row r="4" spans="2:99" s="43" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
+      <c r="B4" s="188"/>
       <c r="C4" s="44"/>
       <c r="D4" s="45" t="s">
         <v>82</v>
@@ -5293,7 +5293,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B5" s="47" t="s">
         <v>86</v>
       </c>
@@ -5502,10 +5502,18 @@
       <c r="BS5" s="59">
         <v>73.707854229661905</v>
       </c>
-      <c r="BT5" s="53"/>
-      <c r="BU5" s="54"/>
-      <c r="BV5" s="54"/>
-      <c r="BW5" s="56"/>
+      <c r="BT5" s="53">
+        <v>670.76041435999991</v>
+      </c>
+      <c r="BU5" s="54">
+        <v>300.1163583</v>
+      </c>
+      <c r="BV5" s="54">
+        <v>300.70605746000001</v>
+      </c>
+      <c r="BW5" s="56">
+        <v>66.918546971660987</v>
+      </c>
       <c r="BX5" s="53"/>
       <c r="BY5" s="54"/>
       <c r="BZ5" s="54"/>
@@ -5531,7 +5539,7 @@
       <c r="CT5" s="54"/>
       <c r="CU5" s="56"/>
     </row>
-    <row r="6" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B6" s="47" t="s">
         <v>87</v>
       </c>
@@ -5740,10 +5748,18 @@
       <c r="BS6" s="59">
         <v>37.730772154580308</v>
       </c>
-      <c r="BT6" s="63"/>
-      <c r="BU6" s="64"/>
-      <c r="BV6" s="64"/>
-      <c r="BW6" s="56"/>
+      <c r="BT6" s="63">
+        <v>271.72558448000001</v>
+      </c>
+      <c r="BU6" s="64">
+        <v>238.61618745999999</v>
+      </c>
+      <c r="BV6" s="64">
+        <v>235.91294554000001</v>
+      </c>
+      <c r="BW6" s="56">
+        <v>34.554134007952669</v>
+      </c>
       <c r="BX6" s="63"/>
       <c r="BY6" s="64"/>
       <c r="BZ6" s="64"/>
@@ -5769,7 +5785,7 @@
       <c r="CT6" s="64"/>
       <c r="CU6" s="56"/>
     </row>
-    <row r="7" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B7" s="47" t="s">
         <v>88</v>
       </c>
@@ -5978,10 +5994,18 @@
       <c r="BS7" s="59">
         <v>225.44584223820402</v>
       </c>
-      <c r="BT7" s="63"/>
-      <c r="BU7" s="64"/>
-      <c r="BV7" s="64"/>
-      <c r="BW7" s="56"/>
+      <c r="BT7" s="63">
+        <v>60.353462059999998</v>
+      </c>
+      <c r="BU7" s="64">
+        <v>14.49951615</v>
+      </c>
+      <c r="BV7" s="64">
+        <v>12.414010339999999</v>
+      </c>
+      <c r="BW7" s="56">
+        <v>145.85164763121986</v>
+      </c>
       <c r="BX7" s="63"/>
       <c r="BY7" s="64"/>
       <c r="BZ7" s="64"/>
@@ -6007,7 +6031,7 @@
       <c r="CT7" s="64"/>
       <c r="CU7" s="56"/>
     </row>
-    <row r="8" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B8" s="47" t="s">
         <v>89</v>
       </c>
@@ -6216,10 +6240,18 @@
       <c r="BS8" s="59">
         <v>77.166771229282404</v>
       </c>
-      <c r="BT8" s="63"/>
-      <c r="BU8" s="64"/>
-      <c r="BV8" s="64"/>
-      <c r="BW8" s="56"/>
+      <c r="BT8" s="63">
+        <v>1126.9385545800001</v>
+      </c>
+      <c r="BU8" s="64">
+        <v>524.73483151999994</v>
+      </c>
+      <c r="BV8" s="64">
+        <v>340.46532509000002</v>
+      </c>
+      <c r="BW8" s="56">
+        <v>99.299852719107335</v>
+      </c>
       <c r="BX8" s="63"/>
       <c r="BY8" s="64"/>
       <c r="BZ8" s="64"/>
@@ -6245,7 +6277,7 @@
       <c r="CT8" s="64"/>
       <c r="CU8" s="56"/>
     </row>
-    <row r="9" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B9" s="47" t="s">
         <v>90</v>
       </c>
@@ -6454,10 +6486,18 @@
       <c r="BS9" s="59">
         <v>111.36164417179326</v>
       </c>
-      <c r="BT9" s="63"/>
-      <c r="BU9" s="64"/>
-      <c r="BV9" s="64"/>
-      <c r="BW9" s="56"/>
+      <c r="BT9" s="63">
+        <v>412.23553404</v>
+      </c>
+      <c r="BU9" s="64">
+        <v>116.47594020999999</v>
+      </c>
+      <c r="BV9" s="64">
+        <v>122.68737979000001</v>
+      </c>
+      <c r="BW9" s="56">
+        <v>100.80145196978128</v>
+      </c>
       <c r="BX9" s="63"/>
       <c r="BY9" s="64"/>
       <c r="BZ9" s="64"/>
@@ -6483,7 +6523,7 @@
       <c r="CT9" s="64"/>
       <c r="CU9" s="56"/>
     </row>
-    <row r="10" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B10" s="47" t="s">
         <v>91</v>
       </c>
@@ -6692,10 +6732,18 @@
       <c r="BS10" s="59">
         <v>176.76455302379873</v>
       </c>
-      <c r="BT10" s="63"/>
-      <c r="BU10" s="64"/>
-      <c r="BV10" s="64"/>
-      <c r="BW10" s="56"/>
+      <c r="BT10" s="63">
+        <v>139.50282657</v>
+      </c>
+      <c r="BU10" s="64">
+        <v>24.398189479999999</v>
+      </c>
+      <c r="BV10" s="64">
+        <v>30.869136329999996</v>
+      </c>
+      <c r="BW10" s="56">
+        <v>135.57505310029515</v>
+      </c>
       <c r="BX10" s="63"/>
       <c r="BY10" s="64"/>
       <c r="BZ10" s="64"/>
@@ -6721,7 +6769,7 @@
       <c r="CT10" s="64"/>
       <c r="CU10" s="56"/>
     </row>
-    <row r="11" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B11" s="47" t="s">
         <v>92</v>
       </c>
@@ -6930,10 +6978,18 @@
       <c r="BS11" s="59">
         <v>32.747904449343409</v>
       </c>
-      <c r="BT11" s="63"/>
-      <c r="BU11" s="64"/>
-      <c r="BV11" s="64"/>
-      <c r="BW11" s="56"/>
+      <c r="BT11" s="63">
+        <v>84.577521919999995</v>
+      </c>
+      <c r="BU11" s="64">
+        <v>81.070604459999998</v>
+      </c>
+      <c r="BV11" s="64">
+        <v>76.071237670000002</v>
+      </c>
+      <c r="BW11" s="56">
+        <v>33.354599390206026</v>
+      </c>
       <c r="BX11" s="63"/>
       <c r="BY11" s="64"/>
       <c r="BZ11" s="64"/>
@@ -6959,7 +7015,7 @@
       <c r="CT11" s="64"/>
       <c r="CU11" s="56"/>
     </row>
-    <row r="12" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B12" s="47" t="s">
         <v>93</v>
       </c>
@@ -7066,7 +7122,9 @@
       <c r="BQ12" s="71"/>
       <c r="BR12" s="71"/>
       <c r="BS12" s="59"/>
-      <c r="BT12" s="63"/>
+      <c r="BT12" s="63">
+        <v>60.591484280000003</v>
+      </c>
       <c r="BU12" s="69"/>
       <c r="BV12" s="69"/>
       <c r="BW12" s="55"/>
@@ -7095,7 +7153,7 @@
       <c r="CT12" s="69"/>
       <c r="CU12" s="55"/>
     </row>
-    <row r="13" spans="2:99" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:99" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="72" t="s">
         <v>94</v>
       </c>
@@ -7202,7 +7260,9 @@
       <c r="BQ13" s="80"/>
       <c r="BR13" s="80"/>
       <c r="BS13" s="81"/>
-      <c r="BT13" s="63"/>
+      <c r="BT13" s="63">
+        <v>-112.57868546</v>
+      </c>
       <c r="BU13" s="76"/>
       <c r="BV13" s="76"/>
       <c r="BW13" s="77"/>
@@ -7231,7 +7291,7 @@
       <c r="CT13" s="76"/>
       <c r="CU13" s="77"/>
     </row>
-    <row r="14" spans="2:99" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:99" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="82" t="s">
         <v>25</v>
       </c>
@@ -7440,10 +7500,18 @@
       <c r="BS14" s="92">
         <v>70.846694167863944</v>
       </c>
-      <c r="BT14" s="84"/>
-      <c r="BU14" s="85"/>
-      <c r="BV14" s="85"/>
-      <c r="BW14" s="88"/>
+      <c r="BT14" s="84">
+        <v>2714.1066968299992</v>
+      </c>
+      <c r="BU14" s="85">
+        <v>1299.9116275799997</v>
+      </c>
+      <c r="BV14" s="85">
+        <v>1119.1260922200001</v>
+      </c>
+      <c r="BW14" s="88">
+        <v>72.756056239723193</v>
+      </c>
       <c r="BX14" s="84"/>
       <c r="BY14" s="85"/>
       <c r="BZ14" s="85"/>
@@ -7469,7 +7537,7 @@
       <c r="CT14" s="85"/>
       <c r="CU14" s="88"/>
     </row>
-    <row r="15" spans="2:99" ht="18" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:99" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B15" s="181" t="s">
         <v>107</v>
       </c>
@@ -7576,7 +7644,9 @@
       <c r="BT15" s="94"/>
       <c r="BU15" s="94"/>
       <c r="BV15" s="94"/>
-      <c r="BW15" s="94"/>
+      <c r="BW15" s="94">
+        <v>572.34285889</v>
+      </c>
       <c r="BX15" s="94"/>
       <c r="BY15" s="94"/>
       <c r="BZ15" s="94"/>
@@ -7602,7 +7672,7 @@
       <c r="CT15" s="94"/>
       <c r="CU15" s="94"/>
     </row>
-    <row r="16" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B16" s="181" t="s">
         <v>108</v>
       </c>
@@ -7724,7 +7794,9 @@
       <c r="BT16" s="96"/>
       <c r="BU16" s="96"/>
       <c r="BV16" s="96"/>
-      <c r="BW16" s="96"/>
+      <c r="BW16" s="96">
+        <v>3515.7535854900002</v>
+      </c>
       <c r="BX16" s="96"/>
       <c r="BY16" s="96"/>
       <c r="BZ16" s="96"/>
@@ -7750,7 +7822,7 @@
       <c r="CT16" s="96"/>
       <c r="CU16" s="96"/>
     </row>
-    <row r="17" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B17" s="181" t="s">
         <v>109</v>
       </c>
@@ -7857,7 +7929,9 @@
       <c r="BT17" s="96"/>
       <c r="BU17" s="96"/>
       <c r="BV17" s="96"/>
-      <c r="BW17" s="96"/>
+      <c r="BW17" s="96">
+        <v>1434.95042115</v>
+      </c>
       <c r="BX17" s="96"/>
       <c r="BY17" s="96"/>
       <c r="BZ17" s="96"/>
@@ -7883,7 +7957,7 @@
       <c r="CT17" s="96"/>
       <c r="CU17" s="96"/>
     </row>
-    <row r="18" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B18" s="181" t="s">
         <v>110</v>
       </c>
@@ -8005,7 +8079,9 @@
       <c r="BT18" s="96"/>
       <c r="BU18" s="96"/>
       <c r="BV18" s="96"/>
-      <c r="BW18" s="96"/>
+      <c r="BW18" s="96">
+        <v>7394.8424441999996</v>
+      </c>
       <c r="BX18" s="96"/>
       <c r="BY18" s="96"/>
       <c r="BZ18" s="96"/>
@@ -8031,7 +8107,7 @@
       <c r="CT18" s="96"/>
       <c r="CU18" s="96"/>
     </row>
-    <row r="19" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B19" s="181" t="s">
         <v>111</v>
       </c>
@@ -8155,7 +8231,9 @@
       <c r="BT19" s="96"/>
       <c r="BU19" s="96"/>
       <c r="BV19" s="96"/>
-      <c r="BW19" s="96"/>
+      <c r="BW19" s="96">
+        <v>0.39885897829927264</v>
+      </c>
       <c r="BX19" s="96"/>
       <c r="BY19" s="96"/>
       <c r="BZ19" s="96"/>
@@ -8181,7 +8259,7 @@
       <c r="CT19" s="96"/>
       <c r="CU19" s="96"/>
     </row>
-    <row r="20" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B20" s="181" t="s">
         <v>112</v>
       </c>
@@ -8305,7 +8383,9 @@
       <c r="BT20" s="96"/>
       <c r="BU20" s="96"/>
       <c r="BV20" s="96"/>
-      <c r="BW20" s="96"/>
+      <c r="BW20" s="96">
+        <v>0.47543319712612847</v>
+      </c>
       <c r="BX20" s="96"/>
       <c r="BY20" s="96"/>
       <c r="BZ20" s="96"/>
@@ -8331,7 +8411,7 @@
       <c r="CT20" s="96"/>
       <c r="CU20" s="96"/>
     </row>
-    <row r="21" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B21" s="95"/>
       <c r="C21" s="95"/>
       <c r="D21" s="96"/>
@@ -8431,7 +8511,7 @@
       <c r="CT21" s="96"/>
       <c r="CU21" s="96"/>
     </row>
-    <row r="22" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B22" s="95"/>
       <c r="C22" s="95"/>
       <c r="D22" s="96"/>
@@ -8531,7 +8611,7 @@
       <c r="CT22" s="96"/>
       <c r="CU22" s="96"/>
     </row>
-    <row r="23" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B23" s="95"/>
       <c r="C23" s="95"/>
       <c r="D23" s="96"/>
@@ -8631,7 +8711,7 @@
       <c r="CT23" s="96"/>
       <c r="CU23" s="96"/>
     </row>
-    <row r="24" spans="2:99" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:99" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="36"/>
       <c r="C24" s="36"/>
       <c r="D24" s="97"/>
@@ -8733,11 +8813,11 @@
       <c r="CT24" s="36"/>
       <c r="CU24" s="36"/>
     </row>
-    <row r="25" spans="2:99" s="111" customFormat="1" ht="18" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="193" t="s">
+    <row r="25" spans="2:99" s="111" customFormat="1" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="187" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="195" t="s">
+      <c r="C25" s="189" t="s">
         <v>16</v>
       </c>
       <c r="D25" s="99" t="str">
@@ -9125,9 +9205,9 @@
         <v>2026-12</v>
       </c>
     </row>
-    <row r="26" spans="2:99" s="111" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="194"/>
-      <c r="C26" s="196"/>
+    <row r="26" spans="2:99" s="111" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="188"/>
+      <c r="C26" s="190"/>
       <c r="D26" s="112" t="s">
         <v>82</v>
       </c>
@@ -9417,7 +9497,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="2:99" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:99" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="117" t="s">
         <v>95</v>
       </c>
@@ -9626,10 +9706,18 @@
       <c r="BS27" s="122">
         <v>66.75710462243616</v>
       </c>
-      <c r="BT27" s="119"/>
-      <c r="BU27" s="120"/>
-      <c r="BV27" s="120"/>
-      <c r="BW27" s="122"/>
+      <c r="BT27" s="119">
+        <v>1303.9544989400001</v>
+      </c>
+      <c r="BU27" s="120">
+        <v>623.72789990000001</v>
+      </c>
+      <c r="BV27" s="120">
+        <v>617.23786242000006</v>
+      </c>
+      <c r="BW27" s="122">
+        <v>63.376920551872587</v>
+      </c>
       <c r="BX27" s="119"/>
       <c r="BY27" s="120"/>
       <c r="BZ27" s="120"/>
@@ -9655,7 +9743,7 @@
       <c r="CT27" s="120"/>
       <c r="CU27" s="122"/>
     </row>
-    <row r="28" spans="2:99" ht="18" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:99" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B28" s="124" t="s">
         <v>86</v>
       </c>
@@ -9866,10 +9954,18 @@
       <c r="BS28" s="59">
         <v>75.80165757408912</v>
       </c>
-      <c r="BT28" s="130"/>
-      <c r="BU28" s="131"/>
-      <c r="BV28" s="131"/>
-      <c r="BW28" s="56"/>
+      <c r="BT28" s="130">
+        <v>564.72698352999998</v>
+      </c>
+      <c r="BU28" s="131">
+        <v>243.50010499999999</v>
+      </c>
+      <c r="BV28" s="131">
+        <v>228.53194838000002</v>
+      </c>
+      <c r="BW28" s="56">
+        <v>74.133221311050022</v>
+      </c>
       <c r="BX28" s="130"/>
       <c r="BY28" s="131"/>
       <c r="BZ28" s="131"/>
@@ -9895,7 +9991,7 @@
       <c r="CT28" s="131"/>
       <c r="CU28" s="56"/>
     </row>
-    <row r="29" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B29" s="124" t="s">
         <v>87</v>
       </c>
@@ -10106,10 +10202,18 @@
       <c r="BS29" s="59">
         <v>28.305454680869374</v>
       </c>
-      <c r="BT29" s="136"/>
-      <c r="BU29" s="137"/>
-      <c r="BV29" s="137"/>
-      <c r="BW29" s="56"/>
+      <c r="BT29" s="136">
+        <v>160.51546222000002</v>
+      </c>
+      <c r="BU29" s="137">
+        <v>177.78718709</v>
+      </c>
+      <c r="BV29" s="137">
+        <v>177.92207554000001</v>
+      </c>
+      <c r="BW29" s="56">
+        <v>27.065016254924473</v>
+      </c>
       <c r="BX29" s="136"/>
       <c r="BY29" s="137"/>
       <c r="BZ29" s="137"/>
@@ -10135,7 +10239,7 @@
       <c r="CT29" s="137"/>
       <c r="CU29" s="56"/>
     </row>
-    <row r="30" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B30" s="124" t="s">
         <v>88</v>
       </c>
@@ -10346,10 +10450,18 @@
       <c r="BS30" s="59">
         <v>225.44584223820402</v>
       </c>
-      <c r="BT30" s="136"/>
-      <c r="BU30" s="137"/>
-      <c r="BV30" s="137"/>
-      <c r="BW30" s="56"/>
+      <c r="BT30" s="136">
+        <v>60.353462059999998</v>
+      </c>
+      <c r="BU30" s="137">
+        <v>14.49951615</v>
+      </c>
+      <c r="BV30" s="137">
+        <v>12.414010339999999</v>
+      </c>
+      <c r="BW30" s="56">
+        <v>145.85164763121986</v>
+      </c>
       <c r="BX30" s="136"/>
       <c r="BY30" s="137"/>
       <c r="BZ30" s="137"/>
@@ -10375,7 +10487,7 @@
       <c r="CT30" s="137"/>
       <c r="CU30" s="56"/>
     </row>
-    <row r="31" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B31" s="124" t="s">
         <v>90</v>
       </c>
@@ -10586,10 +10698,18 @@
       <c r="BS31" s="59">
         <v>113.3883961837561</v>
       </c>
-      <c r="BT31" s="136"/>
-      <c r="BU31" s="137"/>
-      <c r="BV31" s="137"/>
-      <c r="BW31" s="56"/>
+      <c r="BT31" s="136">
+        <v>396.53970656000001</v>
+      </c>
+      <c r="BU31" s="137">
+        <v>110.4759289</v>
+      </c>
+      <c r="BV31" s="137">
+        <v>119.20297349000001</v>
+      </c>
+      <c r="BW31" s="56">
+        <v>99.797772224180108</v>
+      </c>
       <c r="BX31" s="136"/>
       <c r="BY31" s="137"/>
       <c r="BZ31" s="137"/>
@@ -10615,7 +10735,7 @@
       <c r="CT31" s="137"/>
       <c r="CU31" s="56"/>
     </row>
-    <row r="32" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B32" s="124" t="s">
         <v>91</v>
       </c>
@@ -10826,10 +10946,18 @@
       <c r="BS32" s="59">
         <v>128.60344553019169</v>
       </c>
-      <c r="BT32" s="136"/>
-      <c r="BU32" s="137"/>
-      <c r="BV32" s="137"/>
-      <c r="BW32" s="56"/>
+      <c r="BT32" s="136">
+        <v>54.852991939999995</v>
+      </c>
+      <c r="BU32" s="137">
+        <v>13.561514370000001</v>
+      </c>
+      <c r="BV32" s="137">
+        <v>12.808386849999998</v>
+      </c>
+      <c r="BW32" s="56">
+        <v>128.47751847844913</v>
+      </c>
       <c r="BX32" s="136"/>
       <c r="BY32" s="137"/>
       <c r="BZ32" s="137"/>
@@ -10855,7 +10983,7 @@
       <c r="CT32" s="137"/>
       <c r="CU32" s="56"/>
     </row>
-    <row r="33" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B33" s="124" t="s">
         <v>92</v>
       </c>
@@ -11066,10 +11194,18 @@
       <c r="BS33" s="59">
         <v>30.795827034934003</v>
       </c>
-      <c r="BT33" s="141"/>
-      <c r="BU33" s="142"/>
-      <c r="BV33" s="142"/>
-      <c r="BW33" s="56"/>
+      <c r="BT33" s="141">
+        <v>66.965892629999999</v>
+      </c>
+      <c r="BU33" s="142">
+        <v>63.903648390000001</v>
+      </c>
+      <c r="BV33" s="142">
+        <v>66.358467820000001</v>
+      </c>
+      <c r="BW33" s="56">
+        <v>30.274610684945735</v>
+      </c>
       <c r="BX33" s="141"/>
       <c r="BY33" s="142"/>
       <c r="BZ33" s="142"/>
@@ -11095,7 +11231,7 @@
       <c r="CT33" s="142"/>
       <c r="CU33" s="56"/>
     </row>
-    <row r="34" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B34" s="144" t="s">
         <v>97</v>
       </c>
@@ -11306,10 +11442,18 @@
       <c r="BS34" s="148">
         <v>71.670898807851088</v>
       </c>
-      <c r="BT34" s="146"/>
-      <c r="BU34" s="147"/>
-      <c r="BV34" s="147"/>
-      <c r="BW34" s="148"/>
+      <c r="BT34" s="146">
+        <v>728.98918199999991</v>
+      </c>
+      <c r="BU34" s="147">
+        <v>310.65024384999998</v>
+      </c>
+      <c r="BV34" s="147">
+        <v>336.72049050000004</v>
+      </c>
+      <c r="BW34" s="148">
+        <v>64.949048474969459</v>
+      </c>
       <c r="BX34" s="146"/>
       <c r="BY34" s="147"/>
       <c r="BZ34" s="147"/>
@@ -11335,7 +11479,7 @@
       <c r="CT34" s="147"/>
       <c r="CU34" s="148"/>
     </row>
-    <row r="35" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B35" s="124" t="s">
         <v>86</v>
       </c>
@@ -11546,10 +11690,18 @@
       <c r="BS35" s="59">
         <v>78.338663869132986</v>
       </c>
-      <c r="BT35" s="136"/>
-      <c r="BU35" s="137"/>
-      <c r="BV35" s="137"/>
-      <c r="BW35" s="56"/>
+      <c r="BT35" s="136">
+        <v>314.33592807000002</v>
+      </c>
+      <c r="BU35" s="137">
+        <v>131.51927196</v>
+      </c>
+      <c r="BV35" s="137">
+        <v>131.32103054000001</v>
+      </c>
+      <c r="BW35" s="56">
+        <v>71.809349982428188</v>
+      </c>
       <c r="BX35" s="136"/>
       <c r="BY35" s="137"/>
       <c r="BZ35" s="137"/>
@@ -11575,7 +11727,7 @@
       <c r="CT35" s="137"/>
       <c r="CU35" s="56"/>
     </row>
-    <row r="36" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B36" s="124" t="s">
         <v>87</v>
       </c>
@@ -11786,10 +11938,18 @@
       <c r="BS36" s="59">
         <v>32.44584623145149</v>
       </c>
-      <c r="BT36" s="136"/>
-      <c r="BU36" s="137"/>
-      <c r="BV36" s="137"/>
-      <c r="BW36" s="56"/>
+      <c r="BT36" s="136">
+        <v>92.378258630000005</v>
+      </c>
+      <c r="BU36" s="137">
+        <v>94.852021100000002</v>
+      </c>
+      <c r="BV36" s="137">
+        <v>96.000992170000004</v>
+      </c>
+      <c r="BW36" s="56">
+        <v>28.867907469044233</v>
+      </c>
       <c r="BX36" s="136"/>
       <c r="BY36" s="137"/>
       <c r="BZ36" s="137"/>
@@ -11815,7 +11975,7 @@
       <c r="CT36" s="137"/>
       <c r="CU36" s="56"/>
     </row>
-    <row r="37" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B37" s="124" t="s">
         <v>88</v>
       </c>
@@ -12026,10 +12186,18 @@
       <c r="BS37" s="59">
         <v>893.74760293438271</v>
       </c>
-      <c r="BT37" s="136"/>
-      <c r="BU37" s="137"/>
-      <c r="BV37" s="137"/>
-      <c r="BW37" s="56"/>
+      <c r="BT37" s="136">
+        <v>53.375936639999999</v>
+      </c>
+      <c r="BU37" s="137">
+        <v>5.69145E-2</v>
+      </c>
+      <c r="BV37" s="137">
+        <v>2.0519484299999999</v>
+      </c>
+      <c r="BW37" s="56">
+        <v>780.36956279646847</v>
+      </c>
       <c r="BX37" s="136"/>
       <c r="BY37" s="137"/>
       <c r="BZ37" s="137"/>
@@ -12055,7 +12223,7 @@
       <c r="CT37" s="137"/>
       <c r="CU37" s="56"/>
     </row>
-    <row r="38" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B38" s="124" t="s">
         <v>90</v>
       </c>
@@ -12266,10 +12434,18 @@
       <c r="BS38" s="59">
         <v>108.18935229871182</v>
       </c>
-      <c r="BT38" s="136"/>
-      <c r="BU38" s="137"/>
-      <c r="BV38" s="137"/>
-      <c r="BW38" s="56"/>
+      <c r="BT38" s="136">
+        <v>207.96319466</v>
+      </c>
+      <c r="BU38" s="137">
+        <v>44.460632619999998</v>
+      </c>
+      <c r="BV38" s="137">
+        <v>64.300272860000007</v>
+      </c>
+      <c r="BW38" s="56">
+        <v>97.027517338594365</v>
+      </c>
       <c r="BX38" s="136"/>
       <c r="BY38" s="137"/>
       <c r="BZ38" s="137"/>
@@ -12295,7 +12471,7 @@
       <c r="CT38" s="137"/>
       <c r="CU38" s="56"/>
     </row>
-    <row r="39" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B39" s="124" t="s">
         <v>91</v>
       </c>
@@ -12506,10 +12682,18 @@
       <c r="BS39" s="59">
         <v>108.97524639000234</v>
       </c>
-      <c r="BT39" s="136"/>
-      <c r="BU39" s="137"/>
-      <c r="BV39" s="137"/>
-      <c r="BW39" s="56"/>
+      <c r="BT39" s="136">
+        <v>27.977467170000001</v>
+      </c>
+      <c r="BU39" s="137">
+        <v>7.0545412900000004</v>
+      </c>
+      <c r="BV39" s="137">
+        <v>8.5881268399999993</v>
+      </c>
+      <c r="BW39" s="56">
+        <v>97.730742772774434</v>
+      </c>
       <c r="BX39" s="136"/>
       <c r="BY39" s="137"/>
       <c r="BZ39" s="137"/>
@@ -12535,7 +12719,7 @@
       <c r="CT39" s="137"/>
       <c r="CU39" s="56"/>
     </row>
-    <row r="40" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B40" s="124" t="s">
         <v>92</v>
       </c>
@@ -12746,10 +12930,18 @@
       <c r="BS40" s="59">
         <v>29.642574313336404</v>
       </c>
-      <c r="BT40" s="136"/>
-      <c r="BU40" s="137"/>
-      <c r="BV40" s="137"/>
-      <c r="BW40" s="56"/>
+      <c r="BT40" s="136">
+        <v>32.958396829999998</v>
+      </c>
+      <c r="BU40" s="137">
+        <v>32.706862379999997</v>
+      </c>
+      <c r="BV40" s="137">
+        <v>34.458119660000001</v>
+      </c>
+      <c r="BW40" s="56">
+        <v>28.694308182108156</v>
+      </c>
       <c r="BX40" s="136"/>
       <c r="BY40" s="137"/>
       <c r="BZ40" s="137"/>
@@ -12775,7 +12967,7 @@
       <c r="CT40" s="137"/>
       <c r="CU40" s="56"/>
     </row>
-    <row r="41" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B41" s="144" t="s">
         <v>99</v>
       </c>
@@ -12984,10 +13176,18 @@
       <c r="BS41" s="148">
         <v>60.907617083606588</v>
       </c>
-      <c r="BT41" s="146"/>
-      <c r="BU41" s="147"/>
-      <c r="BV41" s="147"/>
-      <c r="BW41" s="148"/>
+      <c r="BT41" s="146">
+        <v>574.96531693999998</v>
+      </c>
+      <c r="BU41" s="147">
+        <v>313.07765605000003</v>
+      </c>
+      <c r="BV41" s="147">
+        <v>280.51737192000002</v>
+      </c>
+      <c r="BW41" s="148">
+        <v>61.48980859951584</v>
+      </c>
       <c r="BX41" s="146"/>
       <c r="BY41" s="147"/>
       <c r="BZ41" s="147"/>
@@ -13013,7 +13213,7 @@
       <c r="CT41" s="147"/>
       <c r="CU41" s="148"/>
     </row>
-    <row r="42" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B42" s="124" t="s">
         <v>86</v>
       </c>
@@ -13224,10 +13424,18 @@
       <c r="BS42" s="59">
         <v>72.664214770635283</v>
       </c>
-      <c r="BT42" s="136"/>
-      <c r="BU42" s="137"/>
-      <c r="BV42" s="137"/>
-      <c r="BW42" s="56"/>
+      <c r="BT42" s="136">
+        <v>250.39105545999999</v>
+      </c>
+      <c r="BU42" s="137">
+        <v>111.98083303999999</v>
+      </c>
+      <c r="BV42" s="137">
+        <v>97.210917839999993</v>
+      </c>
+      <c r="BW42" s="56">
+        <v>77.272510441302515</v>
+      </c>
       <c r="BX42" s="136"/>
       <c r="BY42" s="137"/>
       <c r="BZ42" s="137"/>
@@ -13253,7 +13461,7 @@
       <c r="CT42" s="137"/>
       <c r="CU42" s="56"/>
     </row>
-    <row r="43" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B43" s="124" t="s">
         <v>87</v>
       </c>
@@ -13464,10 +13672,18 @@
       <c r="BS43" s="59">
         <v>23.845139993794355</v>
       </c>
-      <c r="BT43" s="136"/>
-      <c r="BU43" s="137"/>
-      <c r="BV43" s="137"/>
-      <c r="BW43" s="56"/>
+      <c r="BT43" s="136">
+        <v>68.137203589999999</v>
+      </c>
+      <c r="BU43" s="137">
+        <v>82.935165990000002</v>
+      </c>
+      <c r="BV43" s="137">
+        <v>81.921083370000005</v>
+      </c>
+      <c r="BW43" s="56">
+        <v>24.952259218395145</v>
+      </c>
       <c r="BX43" s="136"/>
       <c r="BY43" s="137"/>
       <c r="BZ43" s="137"/>
@@ -13493,7 +13709,7 @@
       <c r="CT43" s="137"/>
       <c r="CU43" s="56"/>
     </row>
-    <row r="44" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B44" s="124" t="s">
         <v>88</v>
       </c>
@@ -13704,10 +13920,18 @@
       <c r="BS44" s="59">
         <v>14.742715268366419</v>
       </c>
-      <c r="BT44" s="136"/>
-      <c r="BU44" s="137"/>
-      <c r="BV44" s="137"/>
-      <c r="BW44" s="56"/>
+      <c r="BT44" s="136">
+        <v>6.9775254200000001</v>
+      </c>
+      <c r="BU44" s="137">
+        <v>14.44260165</v>
+      </c>
+      <c r="BV44" s="137">
+        <v>10.36206191</v>
+      </c>
+      <c r="BW44" s="56">
+        <v>20.201168881068771</v>
+      </c>
       <c r="BX44" s="136"/>
       <c r="BY44" s="137"/>
       <c r="BZ44" s="137"/>
@@ -13733,7 +13957,7 @@
       <c r="CT44" s="137"/>
       <c r="CU44" s="56"/>
     </row>
-    <row r="45" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B45" s="124" t="s">
         <v>90</v>
       </c>
@@ -13944,10 +14168,18 @@
       <c r="BS45" s="59">
         <v>120.84266142968347</v>
       </c>
-      <c r="BT45" s="136"/>
-      <c r="BU45" s="137"/>
-      <c r="BV45" s="137"/>
-      <c r="BW45" s="56"/>
+      <c r="BT45" s="136">
+        <v>188.57651190000001</v>
+      </c>
+      <c r="BU45" s="137">
+        <v>66.015296280000001</v>
+      </c>
+      <c r="BV45" s="137">
+        <v>54.902700629999998</v>
+      </c>
+      <c r="BW45" s="56">
+        <v>103.04220543039617</v>
+      </c>
       <c r="BX45" s="136"/>
       <c r="BY45" s="137"/>
       <c r="BZ45" s="137"/>
@@ -13973,7 +14205,7 @@
       <c r="CT45" s="137"/>
       <c r="CU45" s="56"/>
     </row>
-    <row r="46" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B46" s="124" t="s">
         <v>91</v>
       </c>
@@ -14184,10 +14416,18 @@
       <c r="BS46" s="59">
         <v>164.06995368112734</v>
       </c>
-      <c r="BT46" s="136"/>
-      <c r="BU46" s="137"/>
-      <c r="BV46" s="137"/>
-      <c r="BW46" s="56"/>
+      <c r="BT46" s="136">
+        <v>26.875524769999998</v>
+      </c>
+      <c r="BU46" s="137">
+        <v>6.5069730799999999</v>
+      </c>
+      <c r="BV46" s="137">
+        <v>4.2202600099999996</v>
+      </c>
+      <c r="BW46" s="56">
+        <v>191.04646187427679</v>
+      </c>
       <c r="BX46" s="136"/>
       <c r="BY46" s="137"/>
       <c r="BZ46" s="137"/>
@@ -14213,7 +14453,7 @@
       <c r="CT46" s="137"/>
       <c r="CU46" s="56"/>
     </row>
-    <row r="47" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B47" s="124" t="s">
         <v>92</v>
       </c>
@@ -14424,10 +14664,18 @@
       <c r="BS47" s="59">
         <v>32.042395041692863</v>
       </c>
-      <c r="BT47" s="136"/>
-      <c r="BU47" s="137"/>
-      <c r="BV47" s="137"/>
-      <c r="BW47" s="56"/>
+      <c r="BT47" s="136">
+        <v>34.007495800000001</v>
+      </c>
+      <c r="BU47" s="137">
+        <v>31.19678601</v>
+      </c>
+      <c r="BV47" s="137">
+        <v>31.90034816</v>
+      </c>
+      <c r="BW47" s="56">
+        <v>31.981621920956488</v>
+      </c>
       <c r="BX47" s="136"/>
       <c r="BY47" s="137"/>
       <c r="BZ47" s="137"/>
@@ -14453,7 +14701,7 @@
       <c r="CT47" s="137"/>
       <c r="CU47" s="56"/>
     </row>
-    <row r="48" spans="2:99" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:99" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="117" t="s">
         <v>101</v>
       </c>
@@ -14662,10 +14910,18 @@
       <c r="BS48" s="122">
         <v>86.683560105861901</v>
       </c>
-      <c r="BT48" s="119"/>
-      <c r="BU48" s="120"/>
-      <c r="BV48" s="120"/>
-      <c r="BW48" s="122"/>
+      <c r="BT48" s="119">
+        <v>315.07816317000004</v>
+      </c>
+      <c r="BU48" s="120">
+        <v>133.52477973000001</v>
+      </c>
+      <c r="BV48" s="120">
+        <v>152.46344184</v>
+      </c>
+      <c r="BW48" s="122">
+        <v>61.997451854849203</v>
+      </c>
       <c r="BX48" s="119"/>
       <c r="BY48" s="120"/>
       <c r="BZ48" s="120"/>
@@ -14691,7 +14947,7 @@
       <c r="CT48" s="120"/>
       <c r="CU48" s="122"/>
     </row>
-    <row r="49" spans="2:99" ht="18" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:99" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B49" s="124" t="s">
         <v>86</v>
       </c>
@@ -14902,10 +15158,18 @@
       <c r="BS49" s="59">
         <v>67.250619678026922</v>
       </c>
-      <c r="BT49" s="136"/>
-      <c r="BU49" s="137"/>
-      <c r="BV49" s="137"/>
-      <c r="BW49" s="56"/>
+      <c r="BT49" s="136">
+        <v>100.10915599</v>
+      </c>
+      <c r="BU49" s="137">
+        <v>50.672093949999997</v>
+      </c>
+      <c r="BV49" s="137">
+        <v>72.154224569999997</v>
+      </c>
+      <c r="BW49" s="56">
+        <v>41.622991551747475</v>
+      </c>
       <c r="BX49" s="136"/>
       <c r="BY49" s="137"/>
       <c r="BZ49" s="137"/>
@@ -14931,7 +15195,7 @@
       <c r="CT49" s="137"/>
       <c r="CU49" s="56"/>
     </row>
-    <row r="50" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B50" s="124" t="s">
         <v>87</v>
       </c>
@@ -15142,10 +15406,18 @@
       <c r="BS50" s="59">
         <v>77.179643505092344</v>
       </c>
-      <c r="BT50" s="136"/>
-      <c r="BU50" s="137"/>
-      <c r="BV50" s="137"/>
-      <c r="BW50" s="56"/>
+      <c r="BT50" s="136">
+        <v>109.74980942000001</v>
+      </c>
+      <c r="BU50" s="137">
+        <v>56.951005129999999</v>
+      </c>
+      <c r="BV50" s="137">
+        <v>54.931176409999999</v>
+      </c>
+      <c r="BW50" s="56">
+        <v>59.938535778392961</v>
+      </c>
       <c r="BX50" s="136"/>
       <c r="BY50" s="137"/>
       <c r="BZ50" s="137"/>
@@ -15171,7 +15443,7 @@
       <c r="CT50" s="137"/>
       <c r="CU50" s="56"/>
     </row>
-    <row r="51" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B51" s="124" t="s">
         <v>90</v>
       </c>
@@ -15382,10 +15654,18 @@
       <c r="BS51" s="59">
         <v>101.04642180202092</v>
       </c>
-      <c r="BT51" s="136"/>
-      <c r="BU51" s="137"/>
-      <c r="BV51" s="137"/>
-      <c r="BW51" s="56"/>
+      <c r="BT51" s="136">
+        <v>7.3753129700000004</v>
+      </c>
+      <c r="BU51" s="137">
+        <v>0.62963400000000003</v>
+      </c>
+      <c r="BV51" s="137">
+        <v>1.2652803399999999</v>
+      </c>
+      <c r="BW51" s="56">
+        <v>174.86985461261494</v>
+      </c>
       <c r="BX51" s="136"/>
       <c r="BY51" s="137"/>
       <c r="BZ51" s="137"/>
@@ -15411,7 +15691,7 @@
       <c r="CT51" s="137"/>
       <c r="CU51" s="56"/>
     </row>
-    <row r="52" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B52" s="124" t="s">
         <v>91</v>
       </c>
@@ -15622,10 +15902,18 @@
       <c r="BS52" s="59">
         <v>229.20607678546662</v>
       </c>
-      <c r="BT52" s="136"/>
-      <c r="BU52" s="137"/>
-      <c r="BV52" s="137"/>
-      <c r="BW52" s="56"/>
+      <c r="BT52" s="136">
+        <v>82.841261900000006</v>
+      </c>
+      <c r="BU52" s="137">
+        <v>10.26942376</v>
+      </c>
+      <c r="BV52" s="137">
+        <v>17.8143581</v>
+      </c>
+      <c r="BW52" s="56">
+        <v>139.50757265848384</v>
+      </c>
       <c r="BX52" s="136"/>
       <c r="BY52" s="137"/>
       <c r="BZ52" s="137"/>
@@ -15651,7 +15939,7 @@
       <c r="CT52" s="137"/>
       <c r="CU52" s="56"/>
     </row>
-    <row r="53" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B53" s="124" t="s">
         <v>92</v>
       </c>
@@ -15862,10 +16150,18 @@
       <c r="BS53" s="59">
         <v>35.827460491030564</v>
       </c>
-      <c r="BT53" s="136"/>
-      <c r="BU53" s="137"/>
-      <c r="BV53" s="137"/>
-      <c r="BW53" s="56"/>
+      <c r="BT53" s="136">
+        <v>15.00262289</v>
+      </c>
+      <c r="BU53" s="137">
+        <v>15.00262289</v>
+      </c>
+      <c r="BV53" s="137">
+        <v>6.2984024200000004</v>
+      </c>
+      <c r="BW53" s="56">
+        <v>71.459182295309731</v>
+      </c>
       <c r="BX53" s="136"/>
       <c r="BY53" s="137"/>
       <c r="BZ53" s="137"/>
@@ -15891,7 +16187,7 @@
       <c r="CT53" s="137"/>
       <c r="CU53" s="56"/>
     </row>
-    <row r="54" spans="2:99" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:99" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="117" t="s">
         <v>104</v>
       </c>
@@ -15970,9 +16266,15 @@
         <v>6.6355045699999993</v>
       </c>
       <c r="BS54" s="122"/>
-      <c r="BT54" s="119"/>
-      <c r="BU54" s="120"/>
-      <c r="BV54" s="120"/>
+      <c r="BT54" s="119">
+        <v>20.122681320000005</v>
+      </c>
+      <c r="BU54" s="120">
+        <v>17.924116429999998</v>
+      </c>
+      <c r="BV54" s="120">
+        <v>8.9594628700000012</v>
+      </c>
       <c r="BW54" s="122"/>
       <c r="BX54" s="119"/>
       <c r="BY54" s="120"/>
@@ -15999,7 +16301,7 @@
       <c r="CT54" s="120"/>
       <c r="CU54" s="122"/>
     </row>
-    <row r="55" spans="2:99" ht="18" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:99" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B55" s="124" t="s">
         <v>86</v>
       </c>
@@ -16078,9 +16380,15 @@
         <v>1.42935214</v>
       </c>
       <c r="BS55" s="59"/>
-      <c r="BT55" s="136"/>
-      <c r="BU55" s="137"/>
-      <c r="BV55" s="137"/>
+      <c r="BT55" s="136">
+        <v>5.9242748399999998</v>
+      </c>
+      <c r="BU55" s="137">
+        <v>5.9441593499999996</v>
+      </c>
+      <c r="BV55" s="137">
+        <v>1.9884510000000001E-2</v>
+      </c>
       <c r="BW55" s="56"/>
       <c r="BX55" s="136"/>
       <c r="BY55" s="137"/>
@@ -16107,7 +16415,7 @@
       <c r="CT55" s="137"/>
       <c r="CU55" s="56"/>
     </row>
-    <row r="56" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B56" s="124" t="s">
         <v>87</v>
       </c>
@@ -16186,9 +16494,15 @@
         <v>1.75860942</v>
       </c>
       <c r="BS56" s="59"/>
-      <c r="BT56" s="136"/>
-      <c r="BU56" s="137"/>
-      <c r="BV56" s="137"/>
+      <c r="BT56" s="136">
+        <v>1.4603128400000001</v>
+      </c>
+      <c r="BU56" s="137">
+        <v>3.8779952400000002</v>
+      </c>
+      <c r="BV56" s="137">
+        <v>3.0596935900000002</v>
+      </c>
       <c r="BW56" s="56"/>
       <c r="BX56" s="136"/>
       <c r="BY56" s="137"/>
@@ -16215,7 +16529,7 @@
       <c r="CT56" s="137"/>
       <c r="CU56" s="56"/>
     </row>
-    <row r="57" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B57" s="124" t="s">
         <v>90</v>
       </c>
@@ -16294,9 +16608,15 @@
         <v>3.1237250099999998</v>
       </c>
       <c r="BS57" s="59"/>
-      <c r="BT57" s="136"/>
-      <c r="BU57" s="137"/>
-      <c r="BV57" s="137"/>
+      <c r="BT57" s="136">
+        <v>8.3205145100000006</v>
+      </c>
+      <c r="BU57" s="137">
+        <v>5.3703773100000003</v>
+      </c>
+      <c r="BV57" s="137">
+        <v>2.21912596</v>
+      </c>
       <c r="BW57" s="56"/>
       <c r="BX57" s="136"/>
       <c r="BY57" s="137"/>
@@ -16323,7 +16643,7 @@
       <c r="CT57" s="137"/>
       <c r="CU57" s="56"/>
     </row>
-    <row r="58" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B58" s="124" t="s">
         <v>91</v>
       </c>
@@ -16402,9 +16722,15 @@
         <v>0.32381799999999999</v>
       </c>
       <c r="BS58" s="59"/>
-      <c r="BT58" s="136"/>
-      <c r="BU58" s="137"/>
-      <c r="BV58" s="137"/>
+      <c r="BT58" s="136">
+        <v>1.8085727300000001</v>
+      </c>
+      <c r="BU58" s="137">
+        <v>0.56725135000000004</v>
+      </c>
+      <c r="BV58" s="137">
+        <v>0.24639137999999999</v>
+      </c>
       <c r="BW58" s="56"/>
       <c r="BX58" s="136"/>
       <c r="BY58" s="137"/>
@@ -16431,7 +16757,7 @@
       <c r="CT58" s="137"/>
       <c r="CU58" s="56"/>
     </row>
-    <row r="59" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B59" s="124" t="s">
         <v>92</v>
       </c>
@@ -16510,9 +16836,15 @@
         <v>0</v>
       </c>
       <c r="BS59" s="59"/>
-      <c r="BT59" s="136"/>
-      <c r="BU59" s="137"/>
-      <c r="BV59" s="137"/>
+      <c r="BT59" s="136">
+        <v>2.6090064000000002</v>
+      </c>
+      <c r="BU59" s="137">
+        <v>2.1643331799999999</v>
+      </c>
+      <c r="BV59" s="137">
+        <v>3.41436743</v>
+      </c>
       <c r="BW59" s="56"/>
       <c r="BX59" s="136"/>
       <c r="BY59" s="137"/>
@@ -16539,7 +16871,7 @@
       <c r="CT59" s="137"/>
       <c r="CU59" s="56"/>
     </row>
-    <row r="60" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B60" s="154" t="s">
         <v>89</v>
       </c>
@@ -16748,10 +17080,18 @@
       <c r="BS60" s="158">
         <v>77.166771229282404</v>
       </c>
-      <c r="BT60" s="156"/>
-      <c r="BU60" s="157"/>
-      <c r="BV60" s="157"/>
-      <c r="BW60" s="158"/>
+      <c r="BT60" s="156">
+        <v>1126.9385545800001</v>
+      </c>
+      <c r="BU60" s="157">
+        <v>524.73483151999994</v>
+      </c>
+      <c r="BV60" s="157">
+        <v>340.46532509000002</v>
+      </c>
+      <c r="BW60" s="158">
+        <v>99.299852719107335</v>
+      </c>
       <c r="BX60" s="156"/>
       <c r="BY60" s="157"/>
       <c r="BZ60" s="157"/>
@@ -16777,7 +17117,7 @@
       <c r="CT60" s="157"/>
       <c r="CU60" s="158"/>
     </row>
-    <row r="61" spans="2:99" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B61" s="154" t="s">
         <v>93</v>
       </c>
@@ -16884,7 +17224,9 @@
       <c r="BQ61" s="157"/>
       <c r="BR61" s="157"/>
       <c r="BS61" s="158"/>
-      <c r="BT61" s="161"/>
+      <c r="BT61" s="161">
+        <v>60.591484280000003</v>
+      </c>
       <c r="BU61" s="157"/>
       <c r="BV61" s="157"/>
       <c r="BW61" s="159"/>
@@ -16913,7 +17255,7 @@
       <c r="CT61" s="157"/>
       <c r="CU61" s="159"/>
     </row>
-    <row r="62" spans="2:99" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:99" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="163" t="s">
         <v>105</v>
       </c>
@@ -17020,7 +17362,9 @@
       <c r="BQ62" s="166"/>
       <c r="BR62" s="166"/>
       <c r="BS62" s="167"/>
-      <c r="BT62" s="119"/>
+      <c r="BT62" s="119">
+        <v>-112.57868546</v>
+      </c>
       <c r="BU62" s="166"/>
       <c r="BV62" s="166"/>
       <c r="BW62" s="168"/>
@@ -17049,7 +17393,7 @@
       <c r="CT62" s="166"/>
       <c r="CU62" s="168"/>
     </row>
-    <row r="63" spans="2:99" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:99" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="169" t="s">
         <v>106</v>
       </c>
@@ -17258,10 +17602,18 @@
       <c r="BS63" s="180">
         <v>70.84669416786393</v>
       </c>
-      <c r="BT63" s="175"/>
-      <c r="BU63" s="170"/>
-      <c r="BV63" s="170"/>
-      <c r="BW63" s="176"/>
+      <c r="BT63" s="175">
+        <v>2714.1066968299997</v>
+      </c>
+      <c r="BU63" s="170">
+        <v>1299.91162758</v>
+      </c>
+      <c r="BV63" s="170">
+        <v>1119.1260922200001</v>
+      </c>
+      <c r="BW63" s="176">
+        <v>72.756056239723208</v>
+      </c>
       <c r="BX63" s="175"/>
       <c r="BY63" s="170"/>
       <c r="BZ63" s="170"/>
@@ -17287,7 +17639,7 @@
       <c r="CT63" s="170"/>
       <c r="CU63" s="176"/>
     </row>
-    <row r="64" spans="2:99" ht="18" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="64" spans="2:99" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B3:B4"/>
@@ -17303,58 +17655,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Z24"/>
-  <sheetFormatPr defaultColWidth="3.59765625" defaultRowHeight="13.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.69921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="3.59765625" style="1"/>
+    <col min="1" max="1" width="3.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="3.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:26" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:26" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:26" ht="21" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:26" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:26" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="9"/>
       <c r="Z3" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:26" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B4" s="191"/>
-      <c r="C4" s="187" t="s">
+    <row r="4" spans="2:26" ht="18" x14ac:dyDescent="0.3">
+      <c r="B4" s="195"/>
+      <c r="C4" s="191" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="188"/>
-      <c r="K4" s="188"/>
-      <c r="L4" s="188"/>
-      <c r="M4" s="188"/>
-      <c r="N4" s="189"/>
-      <c r="O4" s="190" t="s">
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="192"/>
+      <c r="K4" s="192"/>
+      <c r="L4" s="192"/>
+      <c r="M4" s="192"/>
+      <c r="N4" s="193"/>
+      <c r="O4" s="194" t="s">
         <v>1</v>
       </c>
-      <c r="P4" s="188"/>
-      <c r="Q4" s="188"/>
-      <c r="R4" s="188"/>
-      <c r="S4" s="188"/>
-      <c r="T4" s="188"/>
-      <c r="U4" s="188"/>
-      <c r="V4" s="188"/>
-      <c r="W4" s="188"/>
-      <c r="X4" s="188"/>
-      <c r="Y4" s="188"/>
-      <c r="Z4" s="189"/>
+      <c r="P4" s="192"/>
+      <c r="Q4" s="192"/>
+      <c r="R4" s="192"/>
+      <c r="S4" s="192"/>
+      <c r="T4" s="192"/>
+      <c r="U4" s="192"/>
+      <c r="V4" s="192"/>
+      <c r="W4" s="192"/>
+      <c r="X4" s="192"/>
+      <c r="Y4" s="192"/>
+      <c r="Z4" s="193"/>
     </row>
-    <row r="5" spans="2:26" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="192"/>
+    <row r="5" spans="2:26" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="196"/>
       <c r="C5" s="2" t="s">
         <v>2</v>
       </c>
@@ -17428,7 +17780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B6" s="23" t="s">
         <v>25</v>
       </c>
@@ -17502,7 +17854,7 @@
       </c>
       <c r="T6" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>112.57868546</v>
       </c>
       <c r="U6" s="25">
         <f t="shared" si="0"/>
@@ -17529,7 +17881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
@@ -17584,7 +17936,9 @@
       <c r="S7" s="12">
         <v>36.005911099999999</v>
       </c>
-      <c r="T7" s="12"/>
+      <c r="T7" s="12">
+        <v>35.2476026</v>
+      </c>
       <c r="U7" s="12"/>
       <c r="V7" s="12"/>
       <c r="W7" s="12"/>
@@ -17592,7 +17946,7 @@
       <c r="Y7" s="12"/>
       <c r="Z7" s="13"/>
     </row>
-    <row r="8" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>19</v>
       </c>
@@ -17647,7 +18001,9 @@
       <c r="S8" s="16">
         <v>43.199071940000003</v>
       </c>
-      <c r="T8" s="16"/>
+      <c r="T8" s="16">
+        <v>41.967093509999998</v>
+      </c>
       <c r="U8" s="16"/>
       <c r="V8" s="16"/>
       <c r="W8" s="16"/>
@@ -17655,7 +18011,7 @@
       <c r="Y8" s="16"/>
       <c r="Z8" s="17"/>
     </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>22</v>
       </c>
@@ -17710,7 +18066,9 @@
       <c r="S9" s="16">
         <v>24.542909030000001</v>
       </c>
-      <c r="T9" s="16"/>
+      <c r="T9" s="16">
+        <v>27.079678149999999</v>
+      </c>
       <c r="U9" s="16"/>
       <c r="V9" s="16"/>
       <c r="W9" s="16"/>
@@ -17718,7 +18076,7 @@
       <c r="Y9" s="16"/>
       <c r="Z9" s="17"/>
     </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>20</v>
       </c>
@@ -17773,7 +18131,9 @@
       <c r="S10" s="16">
         <v>4.1768771899999999</v>
       </c>
-      <c r="T10" s="16"/>
+      <c r="T10" s="16">
+        <v>6.9216218500000002</v>
+      </c>
       <c r="U10" s="16"/>
       <c r="V10" s="16"/>
       <c r="W10" s="16"/>
@@ -17781,7 +18141,7 @@
       <c r="Y10" s="16"/>
       <c r="Z10" s="17"/>
     </row>
-    <row r="11" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="8" t="s">
         <v>21</v>
       </c>
@@ -17836,7 +18196,9 @@
       <c r="S11" s="20">
         <v>1.19266293</v>
       </c>
-      <c r="T11" s="20"/>
+      <c r="T11" s="20">
+        <v>1.3626893499999999</v>
+      </c>
       <c r="U11" s="20"/>
       <c r="V11" s="20"/>
       <c r="W11" s="20"/>
@@ -17844,63 +18206,65 @@
       <c r="Y11" s="20"/>
       <c r="Z11" s="21"/>
     </row>
-    <row r="13" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="14" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="28" t="s">
         <v>26</v>
       </c>
       <c r="C14" s="29">
-        <v>527.64076507000004</v>
+        <v>497.38018162999998</v>
       </c>
       <c r="D14" s="30">
-        <v>532.58967744000006</v>
+        <v>513.60265246999995</v>
       </c>
       <c r="E14" s="30">
-        <v>560.49180527999999</v>
+        <v>526.74811652999995</v>
       </c>
       <c r="F14" s="30">
-        <v>625.47665386000006</v>
+        <v>569.03033723999999</v>
       </c>
       <c r="G14" s="30">
-        <v>611.02664522999999</v>
+        <v>575.72919762000004</v>
       </c>
       <c r="H14" s="30">
-        <v>562.62592627000004</v>
+        <v>565.49809576999996</v>
       </c>
       <c r="I14" s="30">
-        <v>599.30058604999999</v>
+        <v>547.87510239000005</v>
       </c>
       <c r="J14" s="30">
-        <v>553.60944304999987</v>
+        <v>525.89855392000004</v>
       </c>
       <c r="K14" s="30">
-        <v>662.01586393000002</v>
+        <v>651.68759261000002</v>
       </c>
       <c r="L14" s="30">
-        <v>590.06760063000002</v>
+        <v>521.52799333999997</v>
       </c>
       <c r="M14" s="30">
-        <v>605.44808859999989</v>
+        <v>580.86848429999998</v>
       </c>
       <c r="N14" s="31">
-        <v>625.76049417000002</v>
+        <v>594.47652915000003</v>
       </c>
       <c r="O14" s="32">
-        <v>600.76811210000005</v>
+        <v>583.67857376999996</v>
       </c>
       <c r="P14" s="30">
-        <v>574.08240651999995</v>
+        <v>587.65829833999999</v>
       </c>
       <c r="Q14" s="30">
-        <v>571.09232592000001</v>
+        <v>597.07098836</v>
       </c>
       <c r="R14" s="30">
-        <v>610.44356746999995</v>
+        <v>601.50327700000003</v>
       </c>
       <c r="S14" s="30">
-        <v>659.3758551293497</v>
-      </c>
-      <c r="T14" s="30"/>
+        <v>573.49958913</v>
+      </c>
+      <c r="T14" s="30">
+        <v>572.34285889</v>
+      </c>
       <c r="U14" s="30"/>
       <c r="V14" s="30"/>
       <c r="W14" s="30"/>
@@ -17908,8 +18272,8 @@
       <c r="Y14" s="30"/>
       <c r="Z14" s="31"/>
     </row>
-    <row r="15" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="16" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
         <v>27</v>
       </c>
@@ -17964,7 +18328,9 @@
       <c r="S16" s="30">
         <v>54.889426129999997</v>
       </c>
-      <c r="T16" s="33"/>
+      <c r="T16" s="33">
+        <v>60.591484280000003</v>
+      </c>
       <c r="U16" s="33"/>
       <c r="V16" s="33"/>
       <c r="W16" s="33"/>
@@ -17972,7 +18338,7 @@
       <c r="Y16" s="33"/>
       <c r="Z16" s="34"/>
     </row>
-    <row r="17" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="28" t="s">
         <v>28</v>
       </c>
@@ -18035,7 +18401,7 @@
       <c r="Y17" s="33"/>
       <c r="Z17" s="34"/>
     </row>
-    <row r="18" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="28" t="s">
         <v>29</v>
       </c>
@@ -18098,7 +18464,7 @@
       <c r="Y18" s="33"/>
       <c r="Z18" s="34"/>
     </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:26" x14ac:dyDescent="0.3">
       <c r="T19" s="35"/>
       <c r="U19" s="35"/>
       <c r="V19" s="35"/>
@@ -18107,8 +18473,8 @@
       <c r="Y19" s="35"/>
       <c r="Z19" s="35"/>
     </row>
-    <row r="20" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="21" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="28" t="s">
         <v>30</v>
       </c>
@@ -18171,7 +18537,7 @@
       <c r="Y21" s="33"/>
       <c r="Z21" s="34"/>
     </row>
-    <row r="22" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="28" t="s">
         <v>32</v>
       </c>
@@ -18234,7 +18600,7 @@
       <c r="Y22" s="33"/>
       <c r="Z22" s="34"/>
     </row>
-    <row r="23" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="28" t="s">
         <v>31</v>
       </c>
@@ -18263,7 +18629,7 @@
       <c r="Y23" s="30"/>
       <c r="Z23" s="31"/>
     </row>
-    <row r="24" spans="2:26" ht="14.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="28" t="s">
         <v>33</v>
       </c>
